--- a/data/trans_dic/P5_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con algún problema medioambiental importante en la zona de residencia</t>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 29,82</t>
+          <t>12,35; 30,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,34; 52,55</t>
+          <t>20,89; 48,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,91; 43,53</t>
+          <t>22,77; 43,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 6,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 34,87</t>
+          <t>14,63; 34,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,88; 53,57</t>
+          <t>27,8; 54,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,38; 49,58</t>
+          <t>27,3; 49,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 10,9</t>
+          <t>1,25; 11,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,41; 29,37</t>
+          <t>14,88; 29,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,96; 49,34</t>
+          <t>28,1; 47,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,87; 43,58</t>
+          <t>27,35; 43,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,54</t>
+          <t>1,16; 6,79</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,6; 33,99</t>
+          <t>17,04; 33,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,74; 38,99</t>
+          <t>19,94; 39,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,4; 60,05</t>
+          <t>40,36; 59,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,45; 65,5</t>
+          <t>13,53; 68,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,08; 39,63</t>
+          <t>21,09; 40,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,43; 46,65</t>
+          <t>27,01; 46,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,75; 67,74</t>
+          <t>49,04; 67,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 16,45</t>
+          <t>6,34; 16,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,49; 34,07</t>
+          <t>21,3; 33,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,56; 39,67</t>
+          <t>25,8; 39,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,26; 61,11</t>
+          <t>48,34; 61,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 47,32</t>
+          <t>11,75; 51,33</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,84; 43,71</t>
+          <t>24,23; 42,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,1; 63,73</t>
+          <t>40,19; 62,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,63; 36,02</t>
+          <t>17,04; 37,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,68; 31,92</t>
+          <t>14,9; 30,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,99; 41,75</t>
+          <t>23,91; 41,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,98; 57,32</t>
+          <t>36,37; 57,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,94; 39,88</t>
+          <t>21,17; 40,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 31,16</t>
+          <t>14,62; 30,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,82; 39,63</t>
+          <t>26,92; 39,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41,55; 57,19</t>
+          <t>42,26; 57,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,65; 35,5</t>
+          <t>21,23; 35,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 28,87</t>
+          <t>15,97; 28,46</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 35,0</t>
+          <t>16,7; 33,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,14; 43,43</t>
+          <t>21,24; 44,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,46; 45,21</t>
+          <t>20,71; 45,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 24,2</t>
+          <t>9,13; 23,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,13; 32,4</t>
+          <t>16,14; 32,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 36,25</t>
+          <t>15,75; 35,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,86; 45,78</t>
+          <t>23,03; 46,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 23,7</t>
+          <t>6,94; 23,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,7; 29,75</t>
+          <t>18,31; 29,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,25; 36,4</t>
+          <t>20,49; 35,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,29; 41,74</t>
+          <t>25,28; 41,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 21,02</t>
+          <t>9,43; 20,66</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,91; 85,25</t>
+          <t>35,11; 85,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,86; 84,75</t>
+          <t>45,27; 84,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,1; 44,81</t>
+          <t>19,86; 44,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,7</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 65,42</t>
+          <t>18,25; 66,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,93; 77,03</t>
+          <t>45,01; 78,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,44; 53,08</t>
+          <t>26,46; 52,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 7,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,52; 67,35</t>
+          <t>32,63; 67,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,62; 76,07</t>
+          <t>52,16; 75,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,12; 45,62</t>
+          <t>26,68; 45,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,65; 26,08</t>
+          <t>8,58; 25,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,48; 57,54</t>
+          <t>32,19; 57,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,36; 56,92</t>
+          <t>25,44; 57,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,84; 33,23</t>
+          <t>13,45; 32,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 20,95</t>
+          <t>6,2; 21,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,94; 62,22</t>
+          <t>38,98; 62,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,76; 57,22</t>
+          <t>25,87; 57,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 22,98</t>
+          <t>7,82; 23,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,55; 19,94</t>
+          <t>9,22; 20,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39,79; 56,04</t>
+          <t>39,16; 56,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,38; 51,74</t>
+          <t>29,9; 51,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,85; 25,46</t>
+          <t>12,69; 24,47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,23; 35,22</t>
+          <t>21,36; 35,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,16; 53,59</t>
+          <t>38,93; 53,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,24; 43,34</t>
+          <t>29,29; 43,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,21; 42,8</t>
+          <t>27,53; 42,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,52; 34,02</t>
+          <t>20,42; 34,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,09; 53,0</t>
+          <t>37,81; 52,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,04; 43,97</t>
+          <t>30,64; 45,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,69; 44,28</t>
+          <t>28,92; 45,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,59; 32,49</t>
+          <t>22,19; 31,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40,38; 51,09</t>
+          <t>40,01; 50,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,73; 41,9</t>
+          <t>31,9; 41,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,23; 41,0</t>
+          <t>30,4; 41,3</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,2; 44,81</t>
+          <t>28,14; 44,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,61; 31,39</t>
+          <t>18,57; 31,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,99; 37,44</t>
+          <t>25,13; 38,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,72</t>
+          <t>10,03; 20,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,73; 45,7</t>
+          <t>30,74; 45,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,59; 31,46</t>
+          <t>18,91; 31,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,93; 34,95</t>
+          <t>22,69; 34,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,98; 19,29</t>
+          <t>10,19; 19,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,25; 43,11</t>
+          <t>31,75; 43,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,48; 29,43</t>
+          <t>20,15; 28,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25,77; 34,07</t>
+          <t>25,7; 34,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,72</t>
+          <t>11,33; 18,61</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,11; 31,24</t>
+          <t>25,01; 31,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34,46; 41,73</t>
+          <t>34,63; 41,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,61; 38,46</t>
+          <t>31,7; 38,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,9; 31,97</t>
+          <t>17,06; 30,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,8; 31,05</t>
+          <t>24,75; 30,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,77</t>
+          <t>34,62; 41,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,31; 40,94</t>
+          <t>33,9; 40,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,85</t>
+          <t>14,7; 19,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,76; 30,3</t>
+          <t>25,67; 30,21</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35,81; 40,49</t>
+          <t>35,66; 40,63</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,97; 38,42</t>
+          <t>33,78; 38,66</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,67; 25,18</t>
+          <t>16,79; 24,46</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9799</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8876</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14957</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11911</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15235</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19632</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>21710</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24112</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34589</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4518</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5890; 14461</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5298; 12369</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10335; 19809</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4999</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7484; 17504</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10587; 20643</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14193; 25660</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>992; 9024</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>14717; 29140</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17825; 29838</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>26635; 42038</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1766; 10367</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>17052</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15346</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35472</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42694</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19182</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21546</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>47164</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13411</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>36233</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>36892</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>82636</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>56105</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>11569; 22723</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10847; 21378</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28536; 42157</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17276; 87337</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13697; 25987</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>15905; 27612</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>39233; 53800</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>8096; 20903</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>28286; 44924</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>29227; 44599</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>72841; 92269</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>29996; 131019</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>21665</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15052</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12881</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21976</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28264</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19696</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14267</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>43641</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55779</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34748</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>27148</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>15676; 27731</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21183; 33012</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9902; 22008</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8680; 18003</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>16235; 28196</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>21796; 34609</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14009; 26597</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>9819; 20715</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>35699; 52915</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>47604; 64677</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26387; 44086</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>20026; 35700</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>16055</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15649</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14195</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10722</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17164</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13806</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15967</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10885</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>33219</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>29455</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30162</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>21608</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11032; 22339</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10551; 22182</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9100; 19785</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6406; 16684</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11868; 23769</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8735; 19809</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10976; 21999</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5421; 18484</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>25562; 41612</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>21543; 37527</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>23154; 37932</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>13983; 30628</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6067</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12319</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10076</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15163</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14091</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>10487</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>27483</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24167</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3350; 8180</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8168; 15249</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6429; 14480</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2539</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2080; 7569</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11087; 19236</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9398; 18537</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3157</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6833; 14053</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>22257; 32336</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18115; 30979</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3957</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>7447</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19871</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11087</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10496</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6468</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>24975</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>12737</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>13915</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>44846</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>23824</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>18548</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4002; 11711</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14339; 25493</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6941; 15570</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>6211; 15071</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>3241; 11134</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>19306; 31191</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>8113; 17915</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>4392; 13048</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>9125; 20588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>36838; 53525</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>17533; 30310</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>12991; 25047</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>30635</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>53477</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>42460</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>42964</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>29582</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>54982</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>44276</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>57041</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>108459</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>86736</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100006</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>23630; 38848</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>45430; 61901</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>34198; 51068</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>33886; 52846</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>22622; 38709</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>46046; 63711</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>36504; 53918</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>44843; 70014</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>49139; 70718</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>95424; 120300</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>75247; 98773</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>84565; 114882</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>32735</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>28355</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>40164</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>36945</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>32169</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>39830</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>22702</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>69681</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>60524</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>79994</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>42166</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>25373; 40061</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>21453; 36351</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>32581; 50290</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>13207; 27229</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>29689; 44150</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>24674; 41242</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>31584; 48698</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>15974; 30910</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>59297; 80460</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>49580; 71016</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>69113; 92540</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>32682; 53682</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>141455</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>181408</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>183462</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>141069</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>130218</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>289103</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>387550</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>396856</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>271288</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>125887; 158034</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>165150; 199619</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>166203; 201377</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>113404; 205224</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>130804; 162956</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>186550; 224109</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>193596; 231374</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>111905; 149274</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>264926; 311705</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>362249; 412672</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>369934; 423452</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>239320; 348796</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,35; 30,31</t>
+          <t>12,37; 30,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,89; 48,78</t>
+          <t>22,45; 51,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,77; 43,65</t>
+          <t>22,46; 44,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,82</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 34,21</t>
+          <t>13,6; 34,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,8; 54,21</t>
+          <t>26,08; 52,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,3; 49,35</t>
+          <t>27,84; 49,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,37</t>
+          <t>1,16; 10,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 29,47</t>
+          <t>15,58; 29,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,1; 47,03</t>
+          <t>29,58; 49,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,35; 43,17</t>
+          <t>27,72; 43,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,79</t>
+          <t>1,19; 6,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,04; 33,47</t>
+          <t>17,77; 34,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,94; 39,31</t>
+          <t>19,55; 37,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,36; 59,63</t>
+          <t>41,63; 61,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 68,42</t>
+          <t>13,77; 71,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,09; 40,02</t>
+          <t>20,62; 39,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,01; 46,89</t>
+          <t>26,89; 47,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,04; 67,25</t>
+          <t>49,98; 67,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 16,38</t>
+          <t>6,71; 16,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,3; 33,82</t>
+          <t>21,69; 33,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,8; 39,37</t>
+          <t>25,68; 39,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,34; 61,23</t>
+          <t>48,37; 61,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 51,33</t>
+          <t>11,5; 48,76</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,23; 42,86</t>
+          <t>24,36; 44,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,19; 62,63</t>
+          <t>40,76; 63,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,04; 37,87</t>
+          <t>16,88; 36,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 30,9</t>
+          <t>13,37; 30,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,37; 57,75</t>
+          <t>36,81; 57,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 40,19</t>
+          <t>21,58; 40,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,62; 30,84</t>
+          <t>14,53; 30,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,92; 39,91</t>
+          <t>26,7; 40,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,26; 57,42</t>
+          <t>42,1; 57,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,23; 35,47</t>
+          <t>21,15; 34,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,97; 28,46</t>
+          <t>16,08; 27,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,7; 33,82</t>
+          <t>16,4; 34,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,24; 44,65</t>
+          <t>21,1; 42,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,71; 45,02</t>
+          <t>21,4; 45,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 23,79</t>
+          <t>8,71; 25,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,14; 32,33</t>
+          <t>15,64; 32,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,75; 35,71</t>
+          <t>16,29; 35,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,03; 46,17</t>
+          <t>22,72; 45,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 23,66</t>
+          <t>6,93; 25,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 29,81</t>
+          <t>18,18; 29,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,49; 35,69</t>
+          <t>20,78; 35,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,28; 41,41</t>
+          <t>25,42; 40,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 20,66</t>
+          <t>9,5; 21,31</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,11; 85,73</t>
+          <t>34,9; 85,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,27; 84,51</t>
+          <t>47,85; 85,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,86; 44,73</t>
+          <t>19,25; 45,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 9,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,25; 66,4</t>
+          <t>18,12; 64,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,01; 78,1</t>
+          <t>44,18; 77,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,46; 52,19</t>
+          <t>27,84; 54,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,63; 67,11</t>
+          <t>32,56; 69,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52,16; 75,78</t>
+          <t>50,91; 75,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,68; 45,63</t>
+          <t>26,64; 46,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 25,1</t>
+          <t>8,89; 26,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,19; 57,23</t>
+          <t>32,34; 56,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,44; 57,07</t>
+          <t>26,34; 56,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,45; 32,65</t>
+          <t>14,27; 33,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 21,3</t>
+          <t>6,45; 22,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,98; 62,97</t>
+          <t>38,44; 62,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,87; 57,13</t>
+          <t>25,65; 56,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,82; 23,22</t>
+          <t>8,08; 23,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,22; 20,81</t>
+          <t>8,96; 21,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39,16; 56,9</t>
+          <t>39,09; 55,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,9; 51,69</t>
+          <t>30,55; 51,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,69; 24,47</t>
+          <t>13,11; 24,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,36; 35,11</t>
+          <t>20,97; 34,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,93; 53,04</t>
+          <t>38,15; 53,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,29; 43,74</t>
+          <t>29,0; 43,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,53; 42,93</t>
+          <t>28,18; 42,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,42; 34,94</t>
+          <t>19,9; 33,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,81; 52,32</t>
+          <t>37,5; 53,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,64; 45,26</t>
+          <t>30,21; 44,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,92; 45,15</t>
+          <t>29,06; 44,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,19; 31,94</t>
+          <t>22,34; 32,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40,01; 50,44</t>
+          <t>40,24; 50,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,9; 41,87</t>
+          <t>32,0; 42,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,4; 41,3</t>
+          <t>30,16; 41,5</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,14; 44,43</t>
+          <t>28,25; 44,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,57; 31,46</t>
+          <t>17,98; 31,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,13; 38,79</t>
+          <t>25,02; 37,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,03; 20,69</t>
+          <t>9,97; 20,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,74; 45,71</t>
+          <t>30,32; 45,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,91; 31,61</t>
+          <t>18,81; 30,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,69; 34,98</t>
+          <t>22,97; 34,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,19; 19,71</t>
+          <t>9,91; 20,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,75; 43,09</t>
+          <t>31,86; 42,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,15; 28,87</t>
+          <t>20,29; 29,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25,7; 34,42</t>
+          <t>25,52; 34,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,33; 18,61</t>
+          <t>11,27; 18,27</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,01; 31,4</t>
+          <t>24,72; 31,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34,63; 41,85</t>
+          <t>34,52; 41,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,7; 38,41</t>
+          <t>31,79; 38,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,06; 30,87</t>
+          <t>16,81; 32,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,75; 30,83</t>
+          <t>25,14; 31,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,62; 41,6</t>
+          <t>35,17; 41,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,9; 40,52</t>
+          <t>34,37; 40,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,7; 19,61</t>
+          <t>14,54; 19,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,67; 30,21</t>
+          <t>25,75; 30,35</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35,66; 40,63</t>
+          <t>35,53; 40,6</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,78; 38,66</t>
+          <t>33,94; 38,73</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,79; 24,46</t>
+          <t>16,66; 24,06</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5890; 14461</t>
+          <t>5902; 14468</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5298; 12369</t>
+          <t>5693; 12973</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10335; 19809</t>
+          <t>10195; 20255</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4999</t>
+          <t>0; 4507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7484; 17504</t>
+          <t>6961; 17797</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10587; 20643</t>
+          <t>9931; 20074</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14193; 25660</t>
+          <t>14475; 25892</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>992; 9024</t>
+          <t>917; 8382</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14717; 29140</t>
+          <t>15408; 28911</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17825; 29838</t>
+          <t>18762; 31444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26635; 42038</t>
+          <t>26993; 42039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1766; 10367</t>
+          <t>1813; 10354</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11569; 22723</t>
+          <t>12066; 23122</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10847; 21378</t>
+          <t>10630; 20562</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28536; 42157</t>
+          <t>29431; 43188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17276; 87337</t>
+          <t>17575; 91292</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13697; 25987</t>
+          <t>13389; 25802</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15905; 27612</t>
+          <t>15834; 27988</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39233; 53800</t>
+          <t>39979; 53800</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8096; 20903</t>
+          <t>8556; 21390</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28286; 44924</t>
+          <t>28803; 44682</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29227; 44599</t>
+          <t>29088; 44985</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72841; 92269</t>
+          <t>72894; 92225</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29996; 131019</t>
+          <t>29346; 124468</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15676; 27731</t>
+          <t>15761; 28837</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21183; 33012</t>
+          <t>21484; 33549</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9902; 22008</t>
+          <t>9812; 21365</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8680; 18003</t>
+          <t>7789; 17911</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16235; 28196</t>
+          <t>16233; 28196</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21796; 34609</t>
+          <t>22060; 34645</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14009; 26597</t>
+          <t>14280; 26907</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9819; 20715</t>
+          <t>9760; 20525</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35699; 52915</t>
+          <t>35399; 53159</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47604; 64677</t>
+          <t>47424; 64816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26387; 44086</t>
+          <t>26290; 43079</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20026; 35700</t>
+          <t>20165; 34365</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11032; 22339</t>
+          <t>10830; 22740</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10551; 22182</t>
+          <t>10480; 20989</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9100; 19785</t>
+          <t>9404; 19780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6406; 16684</t>
+          <t>6108; 17650</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11868; 23769</t>
+          <t>11501; 23652</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8735; 19809</t>
+          <t>9037; 19840</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10976; 21999</t>
+          <t>10824; 21794</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5421; 18484</t>
+          <t>5417; 19814</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25562; 41612</t>
+          <t>25373; 41830</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21543; 37527</t>
+          <t>21855; 37612</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23154; 37932</t>
+          <t>23286; 37490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13983; 30628</t>
+          <t>14081; 31600</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3350; 8180</t>
+          <t>3330; 8146</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8168; 15249</t>
+          <t>8634; 15336</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6429; 14480</t>
+          <t>6232; 14825</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2539</t>
+          <t>0; 3168</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2080; 7569</t>
+          <t>2065; 7343</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11087; 19236</t>
+          <t>10881; 18985</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9398; 18537</t>
+          <t>9887; 19429</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3157</t>
+          <t>0; 3153</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6833; 14053</t>
+          <t>6819; 14482</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22257; 32336</t>
+          <t>21723; 32370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18115; 30979</t>
+          <t>18083; 31425</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3957</t>
+          <t>0; 3609</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4002; 11711</t>
+          <t>4148; 12445</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14339; 25493</t>
+          <t>14403; 25052</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6941; 15570</t>
+          <t>7187; 15472</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6211; 15071</t>
+          <t>6588; 15532</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3241; 11134</t>
+          <t>3374; 11960</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19306; 31191</t>
+          <t>19042; 30761</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8113; 17915</t>
+          <t>8043; 17620</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4392; 13048</t>
+          <t>4542; 13368</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9125; 20588</t>
+          <t>8867; 21014</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36838; 53525</t>
+          <t>36771; 52430</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17533; 30310</t>
+          <t>17914; 30267</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12991; 25047</t>
+          <t>13414; 25383</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23630; 38848</t>
+          <t>23199; 38709</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45430; 61901</t>
+          <t>44523; 62418</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34198; 51068</t>
+          <t>33862; 50763</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33886; 52846</t>
+          <t>34693; 52291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22622; 38709</t>
+          <t>22043; 36800</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46046; 63711</t>
+          <t>45669; 64607</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36504; 53918</t>
+          <t>35987; 52579</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44843; 70014</t>
+          <t>45057; 69508</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>49139; 70718</t>
+          <t>49458; 71357</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95424; 120300</t>
+          <t>95957; 120623</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75247; 98773</t>
+          <t>75479; 99294</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>84565; 114882</t>
+          <t>83885; 115439</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>25373; 40061</t>
+          <t>25471; 40394</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21453; 36351</t>
+          <t>20776; 36390</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32581; 50290</t>
+          <t>32440; 48561</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13207; 27229</t>
+          <t>13125; 27080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29689; 44150</t>
+          <t>29284; 44155</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24674; 41242</t>
+          <t>24541; 40006</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31584; 48698</t>
+          <t>31975; 48275</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15974; 30910</t>
+          <t>15544; 31578</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>59297; 80460</t>
+          <t>59492; 79914</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49580; 71016</t>
+          <t>49922; 72199</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69113; 92540</t>
+          <t>68629; 93378</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32682; 53682</t>
+          <t>32510; 52687</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>125887; 158034</t>
+          <t>124435; 156383</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>165150; 199619</t>
+          <t>164635; 199800</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>166203; 201377</t>
+          <t>166664; 201612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>113404; 205224</t>
+          <t>111726; 213673</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>130804; 162956</t>
+          <t>132896; 166042</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>186550; 224109</t>
+          <t>189494; 224900</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>193596; 231374</t>
+          <t>196243; 232148</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>111905; 149274</t>
+          <t>110621; 151459</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>264926; 311705</t>
+          <t>265693; 313158</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>362249; 412672</t>
+          <t>360875; 412380</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>369934; 423452</t>
+          <t>371768; 424218</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>239320; 348796</t>
+          <t>237586; 342996</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23,28%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40,01%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,76%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>20,54%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>35,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>32,95%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,76%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,37; 30,33</t>
+          <t>14,6; 34,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,45; 51,16</t>
+          <t>25,88; 53,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,46; 44,63</t>
+          <t>27,38; 49,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,97; 9,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 34,79</t>
+          <t>12,25; 29,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,08; 52,72</t>
+          <t>22,34; 52,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,84; 49,8</t>
+          <t>22,91; 43,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,56</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,58; 29,24</t>
+          <t>16,41; 29,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,58; 49,57</t>
+          <t>28,96; 49,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,72; 43,17</t>
+          <t>27,87; 43,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,78</t>
+          <t>1,12; 6,36</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>58,96%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>25,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>50,17%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>58,96%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,77; 34,06</t>
+          <t>22,08; 39,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,55; 37,81</t>
+          <t>26,43; 46,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,63; 61,08</t>
+          <t>49,75; 67,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 71,52</t>
+          <t>6,12; 16,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,62; 39,74</t>
+          <t>17,6; 33,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,89; 47,53</t>
+          <t>19,74; 38,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,98; 67,25</t>
+          <t>40,4; 60,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 16,76</t>
+          <t>11,65; 27,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,69; 33,64</t>
+          <t>21,49; 34,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,68; 39,71</t>
+          <t>25,56; 39,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,37; 61,2</t>
+          <t>48,26; 61,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 48,76</t>
+          <t>9,79; 18,89</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32,36%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29,76%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>33,49%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>52,2%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>25,9%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,36; 44,57</t>
+          <t>24,99; 41,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,76; 63,64</t>
+          <t>35,98; 57,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,88; 36,76</t>
+          <t>20,94; 39,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,37; 30,74</t>
+          <t>13,83; 30,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,91; 41,52</t>
+          <t>23,84; 43,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,81; 57,81</t>
+          <t>41,1; 63,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,58; 40,66</t>
+          <t>16,63; 36,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 30,56</t>
+          <t>14,36; 31,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,7; 40,09</t>
+          <t>25,82; 39,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,1; 57,54</t>
+          <t>41,55; 57,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,15; 34,66</t>
+          <t>21,65; 35,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,08; 27,4</t>
+          <t>15,95; 28,05</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23,35%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>24,31%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>31,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>32,3%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,4; 34,43</t>
+          <t>16,13; 32,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,1; 42,25</t>
+          <t>16,12; 36,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,4; 45,01</t>
+          <t>22,86; 45,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 25,16</t>
+          <t>7,23; 24,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 32,17</t>
+          <t>17,01; 35,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,29; 35,77</t>
+          <t>21,14; 43,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,72; 45,74</t>
+          <t>21,46; 45,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 25,36</t>
+          <t>8,68; 24,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 29,97</t>
+          <t>18,7; 29,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,78; 35,77</t>
+          <t>21,25; 36,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,42; 40,93</t>
+          <t>25,29; 41,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 21,31</t>
+          <t>9,74; 21,59</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38,77%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61,57%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39,68%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>63,59%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>68,28%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>31,12%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>39,68%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,9; 85,38</t>
+          <t>18,5; 65,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,85; 85,0</t>
+          <t>44,93; 77,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,25; 45,79</t>
+          <t>26,44; 53,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,12; 64,42</t>
+          <t>34,91; 85,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,18; 77,08</t>
+          <t>46,86; 84,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,84; 54,7</t>
+          <t>19,1; 44,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,56; 69,16</t>
+          <t>32,52; 67,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,91; 75,86</t>
+          <t>50,62; 76,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,64; 46,29</t>
+          <t>27,12; 45,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>50,42%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40,62%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14,68%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15,96%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>44,61%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>40,64%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,37%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,62%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,89; 26,67</t>
+          <t>7,09; 20,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,34; 56,24</t>
+          <t>37,94; 62,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,34; 56,71</t>
+          <t>27,76; 57,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,27; 33,64</t>
+          <t>7,9; 23,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 22,88</t>
+          <t>8,65; 26,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,44; 62,1</t>
+          <t>32,48; 57,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,65; 56,19</t>
+          <t>26,36; 56,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 23,79</t>
+          <t>13,68; 32,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,96; 21,24</t>
+          <t>8,55; 19,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39,09; 55,73</t>
+          <t>39,79; 56,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,55; 51,62</t>
+          <t>30,38; 51,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,11; 24,8</t>
+          <t>13,24; 25,93</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26,7%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45,15%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37,17%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>38,47%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>27,69%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>45,82%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>36,36%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34,9%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26,7%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,17%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,97; 34,98</t>
+          <t>20,52; 34,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,15; 53,48</t>
+          <t>38,09; 53,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,0; 43,47</t>
+          <t>30,04; 43,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,18; 42,48</t>
+          <t>30,81; 46,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,9; 33,22</t>
+          <t>21,23; 35,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,5; 53,05</t>
+          <t>38,16; 53,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,21; 44,14</t>
+          <t>29,24; 43,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,06; 44,82</t>
+          <t>26,98; 41,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,34; 32,23</t>
+          <t>22,59; 32,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40,24; 50,58</t>
+          <t>40,38; 51,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32,0; 42,09</t>
+          <t>31,73; 41,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,16; 41,5</t>
+          <t>31,45; 41,79</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>38,25%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24,66%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>36,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>24,54%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>30,98%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>38,25%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,25; 44,8</t>
+          <t>30,73; 45,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,98; 31,5</t>
+          <t>18,59; 31,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,02; 37,45</t>
+          <t>22,93; 34,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,97; 20,57</t>
+          <t>9,5; 18,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,32; 45,72</t>
+          <t>28,2; 44,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,81; 30,66</t>
+          <t>18,61; 31,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,97; 34,67</t>
+          <t>24,99; 37,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,91; 20,14</t>
+          <t>9,56; 19,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,86; 42,79</t>
+          <t>31,25; 43,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,29; 29,35</t>
+          <t>20,48; 29,43</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25,52; 34,73</t>
+          <t>25,77; 34,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,27; 18,27</t>
+          <t>10,99; 17,92</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>28,1%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>35,0%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24,72; 31,07</t>
+          <t>24,8; 31,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34,52; 41,89</t>
+          <t>34,92; 41,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,79; 38,46</t>
+          <t>34,31; 40,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,81; 32,14</t>
+          <t>15,07; 20,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,14; 31,41</t>
+          <t>25,11; 31,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,17; 41,74</t>
+          <t>34,46; 41,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,37; 40,65</t>
+          <t>31,61; 38,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,9</t>
+          <t>16,01; 21,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,75; 30,35</t>
+          <t>25,76; 30,3</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35,53; 40,6</t>
+          <t>35,81; 40,49</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,94; 38,73</t>
+          <t>33,97; 38,42</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,66; 24,06</t>
+          <t>16,11; 19,86</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11911</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15235</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19632</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2463</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>9799</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>8876</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>14957</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1281</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11911</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15235</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19632</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>3583</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5902; 14468</t>
+          <t>7470; 17843</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5693; 12973</t>
+          <t>9855; 20398</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10195; 20255</t>
+          <t>14236; 25777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4507</t>
+          <t>622; 5918</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6961; 17797</t>
+          <t>5844; 14227</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9931; 20074</t>
+          <t>5666; 13325</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14475; 25892</t>
+          <t>10396; 19754</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>917; 8382</t>
+          <t>0; 4413</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15408; 28911</t>
+          <t>16227; 29039</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18762; 31444</t>
+          <t>18370; 31301</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26993; 42039</t>
+          <t>27144; 42441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1813; 10354</t>
+          <t>1349; 7667</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19182</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21546</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47164</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11990</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>17052</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>15346</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42694</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19182</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21546</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47164</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56105</t>
+          <t>30563</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12066; 23122</t>
+          <t>14340; 25731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10630; 20562</t>
+          <t>15563; 27468</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29431; 43188</t>
+          <t>39795; 54187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17575; 91292</t>
+          <t>7090; 18926</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13389; 25802</t>
+          <t>11946; 23073</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15834; 27988</t>
+          <t>10736; 21206</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39979; 53800</t>
+          <t>28561; 42456</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8556; 21390</t>
+          <t>11816; 28247</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28803; 44682</t>
+          <t>28537; 45250</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29088; 44985</t>
+          <t>28956; 44932</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72894; 92225</t>
+          <t>72725; 92089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29346; 124468</t>
+          <t>21262; 41025</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21976</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28264</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19696</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12526</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>21665</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>27515</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>15052</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12881</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21976</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28264</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>19696</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>24669</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15761; 28837</t>
+          <t>16971; 28347</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21484; 33549</t>
+          <t>21564; 34354</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9812; 21365</t>
+          <t>13856; 26389</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7789; 17911</t>
+          <t>8214; 18374</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16233; 28196</t>
+          <t>15426; 28280</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22060; 34645</t>
+          <t>21664; 33592</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14280; 26907</t>
+          <t>9661; 20930</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9760; 20525</t>
+          <t>8123; 17892</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35399; 53159</t>
+          <t>34234; 52547</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47424; 64816</t>
+          <t>46806; 64419</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26290; 43079</t>
+          <t>26912; 44129</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20165; 34365</t>
+          <t>18492; 32516</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17164</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13806</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15967</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>16055</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15649</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>14195</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10722</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17164</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13806</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15967</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21546</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10830; 22740</t>
+          <t>11857; 23822</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10480; 20989</t>
+          <t>8942; 20107</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9404; 19780</t>
+          <t>10892; 21813</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6108; 17650</t>
+          <t>5220; 17765</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11501; 23652</t>
+          <t>11233; 23116</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9037; 19840</t>
+          <t>10502; 21574</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10824; 21794</t>
+          <t>9433; 19868</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5417; 19814</t>
+          <t>6151; 17095</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25373; 41830</t>
+          <t>26100; 41526</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21855; 37612</t>
+          <t>22348; 38276</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23286; 37490</t>
+          <t>23167; 38232</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14081; 31600</t>
+          <t>13922; 30868</t>
         </is>
       </c>
     </row>
@@ -2905,37 +2905,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15163</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14091</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>6067</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>12319</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>10076</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4420</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15163</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14091</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>637</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1267</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3330; 8146</t>
+          <t>2109; 7457</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8634; 15336</t>
+          <t>11065; 18973</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6232; 14825</t>
+          <t>9389; 18852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3168</t>
+          <t>0; 3102</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2065; 7343</t>
+          <t>3331; 8133</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10881; 18985</t>
+          <t>8456; 15292</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9887; 19429</t>
+          <t>6183; 14508</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3153</t>
+          <t>0; 2631</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6819; 14482</t>
+          <t>6809; 14103</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21723; 32370</t>
+          <t>21601; 32461</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18083; 31425</t>
+          <t>18409; 30971</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3609</t>
+          <t>0; 4505</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6468</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24975</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12737</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7183</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>7447</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>19871</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>11087</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10496</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6468</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>24975</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12737</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>17468</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4148; 12445</t>
+          <t>3705; 10951</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14403; 25052</t>
+          <t>18795; 30819</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7187; 15472</t>
+          <t>8704; 17943</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6588; 15532</t>
+          <t>3866; 11498</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3374; 11960</t>
+          <t>4034; 12170</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19042; 30761</t>
+          <t>14468; 25629</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8043; 17620</t>
+          <t>7191; 15530</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4542; 13368</t>
+          <t>6261; 14969</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8867; 21014</t>
+          <t>8458; 19731</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36771; 52430</t>
+          <t>37436; 52722</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17914; 30267</t>
+          <t>17812; 30338</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13414; 25383</t>
+          <t>12540; 24558</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>29582</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>54982</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>44276</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>54021</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>30635</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>53477</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>42460</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>42964</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>29582</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>54982</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44276</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>57041</t>
+          <t>42288</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>100006</t>
+          <t>96309</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23199; 38709</t>
+          <t>22735; 37686</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44523; 62418</t>
+          <t>46386; 64537</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33862; 50763</t>
+          <t>35780; 52380</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34693; 52291</t>
+          <t>43254; 64707</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22043; 36800</t>
+          <t>23496; 38974</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45669; 64607</t>
+          <t>44540; 62536</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35987; 52579</t>
+          <t>34142; 50607</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>45057; 69508</t>
+          <t>32919; 51231</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>49458; 71357</t>
+          <t>50029; 71946</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95957; 120623</t>
+          <t>96293; 121836</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75479; 99294</t>
+          <t>74848; 98844</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>83885; 115439</t>
+          <t>82526; 109684</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>36945</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>32169</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>39830</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>22080</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>32735</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>28355</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>40164</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>19463</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>36945</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>32169</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>39830</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>41771</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>25471; 40394</t>
+          <t>29682; 44137</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20776; 36390</t>
+          <t>24260; 41049</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32440; 48561</t>
+          <t>31921; 48660</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13125; 27080</t>
+          <t>15148; 30193</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29284; 44155</t>
+          <t>25427; 40401</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24541; 40006</t>
+          <t>21497; 36265</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31975; 48275</t>
+          <t>32400; 48543</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15544; 31578</t>
+          <t>13431; 27527</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>59492; 79914</t>
+          <t>58353; 80505</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49922; 72199</t>
+          <t>50376; 72401</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>68629; 93378</t>
+          <t>69297; 91611</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32510; 52687</t>
+          <t>32949; 53739</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>168</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>121544</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>141455</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>181408</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>183462</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>147647</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>206142</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>213394</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>271288</t>
+          <t>237175</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>124435; 156383</t>
+          <t>131055; 164091</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>164635; 199800</t>
+          <t>188165; 225055</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>166664; 201612</t>
+          <t>195913; 233758</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111726; 213673</t>
+          <t>105481; 140487</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>132896; 166042</t>
+          <t>126371; 157231</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>189494; 224900</t>
+          <t>164366; 199035</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>196243; 232148</t>
+          <t>165689; 201641</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>110621; 151459</t>
+          <t>100715; 134229</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>265693; 313158</t>
+          <t>265826; 312670</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>360875; 412380</t>
+          <t>363763; 411236</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>371768; 424218</t>
+          <t>372034; 420792</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>237586; 342996</t>
+          <t>214098; 263885</t>
         </is>
       </c>
     </row>
